--- a/data/raw/Documentation.xlsx
+++ b/data/raw/Documentation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noemivillars-amberg/Documents/daschland-scripts/data/spreadsheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noemivillars-amberg/Documents/Customer_Projects/daschland-scripts/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D894341D-2BB0-4547-A781-31FB00449354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A136643F-E746-6649-A1AF-D3F1BCE9B7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="64340" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1780" yWindow="840" windowWidth="64340" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -62,64 +62,49 @@
     <t>DOC_001</t>
   </si>
   <si>
-    <t>DaSCHland_Data_Model.pdf</t>
-  </si>
-  <si>
-    <t>Visualisations of the data model of project Alice in DaSCHland, with details of classes and properties</t>
-  </si>
-  <si>
     <t>DaSCH</t>
   </si>
   <si>
     <t>CC BY 4.0</t>
   </si>
   <si>
-    <t>https://app.rdu-08.dasch.swiss/resource/0854/pBVr6wmvTIORGGr0ut4Uxg</t>
-  </si>
-  <si>
     <t>Noémi Villars-Amberg</t>
   </si>
   <si>
     <t>DOC_002</t>
   </si>
   <si>
-    <t>DaSCHland_Data_Model_Links.pdf</t>
-  </si>
-  <si>
-    <t>Visualisations of the data model, with links between the classes</t>
-  </si>
-  <si>
-    <t>https://app.rdu-08.dasch.swiss/resource/0854/-HwOlsp4QJ-2ZgNr10MDDw</t>
-  </si>
-  <si>
     <t>DOC_003</t>
   </si>
   <si>
-    <t>DaSCHland_Data_Model_Legend.pdf</t>
-  </si>
-  <si>
-    <t>Legend to the Visualisations of the data model</t>
-  </si>
-  <si>
-    <t>https://app.rdu-08.dasch.swiss/resource/0854/ZOIhp5PZTtujDK0-kWGM6Q</t>
-  </si>
-  <si>
     <t>DOC_004</t>
   </si>
   <si>
-    <t>DaSCHland FAQ.pdf</t>
-  </si>
-  <si>
-    <t>Frequent asked questions to the DaSCH project Alice in DaSCHland</t>
-  </si>
-  <si>
-    <t>https://app.rdu-08.dasch.swiss/resource/0854/jI8CCsGYRfmgLqT5d6H1jA</t>
-  </si>
-  <si>
     <t>Authorship Resource</t>
   </si>
   <si>
-    <t>Daniela Subotic, Noémi Villars-Amberg</t>
+    <t>Alice_in_DaSCHland_api_search_documentation.pdf</t>
+  </si>
+  <si>
+    <t>Alice_in_DaSCHland_database_documentation.pdf</t>
+  </si>
+  <si>
+    <t>Alice_in_DaSCHland_general_documentation.pdf</t>
+  </si>
+  <si>
+    <t>Alice_in_DaSCHland_search_documentation.pdf</t>
+  </si>
+  <si>
+    <t>Document explaining how the api search works for the project, with examples.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document explaining how the database is built, with description of each class and property as well as visualisations of the data model. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">General documentation about the project, explaining what data is to be found, how it was collected and what is specific about it. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document explaining how to search for data in the project. </t>
   </si>
 </sst>
 </file>
@@ -379,7 +364,7 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="42.1640625" customWidth="1"/>
+    <col min="2" max="2" width="51.6640625" customWidth="1"/>
     <col min="3" max="3" width="70.1640625" customWidth="1"/>
     <col min="4" max="4" width="11.5" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
@@ -410,124 +395,110 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F5" s="2"/>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/data/raw/Documentation.xlsx
+++ b/data/raw/Documentation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noemivillars-amberg/Documents/Customer_Projects/daschland-scripts/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A136643F-E746-6649-A1AF-D3F1BCE9B7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A22C28-A73B-A140-9E58-92EE4EA19B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1780" yWindow="840" windowWidth="64340" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7000" yWindow="5040" windowWidth="64340" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,9 +95,6 @@
     <t>Alice_in_DaSCHland_search_documentation.pdf</t>
   </si>
   <si>
-    <t>Document explaining how the api search works for the project, with examples.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Document explaining how the database is built, with description of each class and property as well as visualisations of the data model. </t>
   </si>
   <si>
@@ -105,13 +102,16 @@
   </si>
   <si>
     <t xml:space="preserve">Document explaining how to search for data in the project. </t>
+  </si>
+  <si>
+    <t>Document explaining how to explore and retrieve information via the REST API</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -123,6 +123,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Menlo"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -146,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -154,6 +160,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -405,8 +412,8 @@
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
+      <c r="C2" s="3" t="s">
+        <v>22</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
@@ -430,7 +437,7 @@
         <v>16</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>8</v>
@@ -454,7 +461,7 @@
         <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
@@ -478,7 +485,7 @@
         <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>8</v>

--- a/data/raw/Documentation.xlsx
+++ b/data/raw/Documentation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noemivillars-amberg/Documents/daschland-scripts/data/spreadsheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/noemivillars-amberg/Documents/Customer_Projects/daschland-scripts/data/raw/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D894341D-2BB0-4547-A781-31FB00449354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A22C28-A73B-A140-9E58-92EE4EA19B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="64340" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7000" yWindow="5040" windowWidth="64340" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
   <si>
     <t>ID</t>
   </si>
@@ -62,71 +62,56 @@
     <t>DOC_001</t>
   </si>
   <si>
-    <t>DaSCHland_Data_Model.pdf</t>
-  </si>
-  <si>
-    <t>Visualisations of the data model of project Alice in DaSCHland, with details of classes and properties</t>
-  </si>
-  <si>
     <t>DaSCH</t>
   </si>
   <si>
     <t>CC BY 4.0</t>
   </si>
   <si>
-    <t>https://app.rdu-08.dasch.swiss/resource/0854/pBVr6wmvTIORGGr0ut4Uxg</t>
-  </si>
-  <si>
     <t>Noémi Villars-Amberg</t>
   </si>
   <si>
     <t>DOC_002</t>
   </si>
   <si>
-    <t>DaSCHland_Data_Model_Links.pdf</t>
-  </si>
-  <si>
-    <t>Visualisations of the data model, with links between the classes</t>
-  </si>
-  <si>
-    <t>https://app.rdu-08.dasch.swiss/resource/0854/-HwOlsp4QJ-2ZgNr10MDDw</t>
-  </si>
-  <si>
     <t>DOC_003</t>
   </si>
   <si>
-    <t>DaSCHland_Data_Model_Legend.pdf</t>
-  </si>
-  <si>
-    <t>Legend to the Visualisations of the data model</t>
-  </si>
-  <si>
-    <t>https://app.rdu-08.dasch.swiss/resource/0854/ZOIhp5PZTtujDK0-kWGM6Q</t>
-  </si>
-  <si>
     <t>DOC_004</t>
   </si>
   <si>
-    <t>DaSCHland FAQ.pdf</t>
-  </si>
-  <si>
-    <t>Frequent asked questions to the DaSCH project Alice in DaSCHland</t>
-  </si>
-  <si>
-    <t>https://app.rdu-08.dasch.swiss/resource/0854/jI8CCsGYRfmgLqT5d6H1jA</t>
-  </si>
-  <si>
     <t>Authorship Resource</t>
   </si>
   <si>
-    <t>Daniela Subotic, Noémi Villars-Amberg</t>
+    <t>Alice_in_DaSCHland_api_search_documentation.pdf</t>
+  </si>
+  <si>
+    <t>Alice_in_DaSCHland_database_documentation.pdf</t>
+  </si>
+  <si>
+    <t>Alice_in_DaSCHland_general_documentation.pdf</t>
+  </si>
+  <si>
+    <t>Alice_in_DaSCHland_search_documentation.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document explaining how the database is built, with description of each class and property as well as visualisations of the data model. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">General documentation about the project, explaining what data is to be found, how it was collected and what is specific about it. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Document explaining how to search for data in the project. </t>
+  </si>
+  <si>
+    <t>Document explaining how to explore and retrieve information via the REST API</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -138,6 +123,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF1F2328"/>
+      <name val="Menlo"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -161,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -169,6 +160,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -379,7 +371,7 @@
   <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="42.1640625" customWidth="1"/>
+    <col min="2" max="2" width="51.6640625" customWidth="1"/>
     <col min="3" max="3" width="70.1640625" customWidth="1"/>
     <col min="4" max="4" width="11.5" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
@@ -410,124 +402,110 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="34" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F5" s="2"/>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H5" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">
-    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>